--- a/activityAnalysis/Retired_officials.xlsx
+++ b/activityAnalysis/Retired_officials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rachaelnaphtal/Documents/JudgingAnalysis/activityAnalysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC497A2A-5CFC-0844-84FB-433FDCA610AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C908D6B1-495E-9D42-B687-470450525022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12760" yWindow="760" windowWidth="14480" windowHeight="16740" xr2:uid="{60371592-3745-1D41-9708-B8EF80DEDAF7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="211">
   <si>
     <t>Adrienne Doddy</t>
   </si>
@@ -657,6 +657,18 @@
   </si>
   <si>
     <t>A Neale</t>
+  </si>
+  <si>
+    <t>Krissa Price</t>
+  </si>
+  <si>
+    <t>Wendy Mlinar</t>
+  </si>
+  <si>
+    <t>Kristy Panos</t>
+  </si>
+  <si>
+    <t>Elizabeth Barrow</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39850149-7C44-0145-B92C-8CF5EF556C27}">
-  <dimension ref="A1:A213"/>
+  <dimension ref="A1:A217"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -2078,6 +2090,26 @@
         <v>205</v>
       </c>
     </row>
+    <row r="214" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A214" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A215" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A216" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A217" t="s">
+        <v>210</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
